--- a/data/trans_bre/P16A11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 3,6</t>
+          <t>-5,02; 3,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -1,83</t>
+          <t>-12,39; -1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,94</t>
+          <t>-8,3; 2,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -4,74</t>
+          <t>-14,17; -5,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 39,03</t>
+          <t>-38,5; 43,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,74; -12,17</t>
+          <t>-66,21; -9,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 19,2</t>
+          <t>-56,45; 21,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,44; -26,33</t>
+          <t>-58,72; -29,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -2,44</t>
+          <t>-11,98; -3,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 1,17</t>
+          <t>-8,18; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -2,28</t>
+          <t>-11,35; -2,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,77; -3,85</t>
+          <t>-12,26; -3,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,99; -21,79</t>
+          <t>-75,45; -29,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,91; 10,79</t>
+          <t>-54,71; 16,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,75; -17,86</t>
+          <t>-69,06; -17,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,18; -20,97</t>
+          <t>-53,09; -21,8</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 8,76</t>
+          <t>-3,19; 8,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 7,61</t>
+          <t>-4,98; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 12,09</t>
+          <t>-2,28; 13,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 21,93</t>
+          <t>0,87; 22,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 85,69</t>
+          <t>-26,09; 80,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 40,79</t>
+          <t>-21,08; 38,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 80,83</t>
+          <t>-13,37; 86,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 398,27</t>
+          <t>1,67; 381,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,75</t>
+          <t>-5,56; 0,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; -4,31</t>
+          <t>-11,23; -4,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -4,09</t>
+          <t>-10,13; -4,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 42,29</t>
+          <t>-6,43; 43,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 5,24</t>
+          <t>-31,74; 4,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -26,02</t>
+          <t>-54,94; -25,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,73; -23,91</t>
+          <t>-52,26; -23,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 206,62</t>
+          <t>-29,48; 226,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,98</t>
+          <t>-2,21; 7,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 11,1</t>
+          <t>1,81; 11,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,82</t>
+          <t>-2,0; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 9,79</t>
+          <t>-2,64; 9,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 69,57</t>
+          <t>-14,98; 73,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 69,75</t>
+          <t>8,39; 74,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 46,68</t>
+          <t>-11,03; 42,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 54,79</t>
+          <t>-9,06; 54,02</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,0; 25,57</t>
+          <t>20,27; 25,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,85; 33,34</t>
+          <t>26,75; 32,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,35; 30,22</t>
+          <t>24,15; 30,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,29; 31,29</t>
+          <t>25,26; 30,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>555,28; 4032,34</t>
+          <t>629,73; 4200,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>785,51; 8460,11</t>
+          <t>813,38; 8331,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>829,47; 11692,85</t>
+          <t>750,81; 7885,53</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,83</t>
+          <t>2,38; 5,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,26</t>
+          <t>2,08; 6,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,58</t>
+          <t>0,92; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,48</t>
+          <t>1,16; 22,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 48,7</t>
+          <t>17,83; 49,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,28; 39,89</t>
+          <t>11,75; 39,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 32,29</t>
+          <t>5,85; 33,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 138,8</t>
+          <t>5,93; 134,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,11</t>
+          <t>-7,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-44,49%</t>
+          <t>-39,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,76</t>
+          <t>-5,08; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -1,53</t>
+          <t>-12,17; -1,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,22</t>
+          <t>-7,63; 2,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -5,59</t>
+          <t>-11,92; -4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 43,05</t>
+          <t>-40,74; 42,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,21; -9,14</t>
+          <t>-64,78; -7,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 21,8</t>
+          <t>-52,06; 22,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,72; -29,61</t>
+          <t>-53,43; -23,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,29</t>
+          <t>-7,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,04%</t>
+          <t>-36,6%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -3,48</t>
+          <t>-11,74; -3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,65</t>
+          <t>-8,1; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -2,02</t>
+          <t>-11,65; -2,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -3,91</t>
+          <t>-12,28; -3,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -29,27</t>
+          <t>-73,96; -26,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 16,66</t>
+          <t>-52,82; 13,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,06; -17,6</t>
+          <t>-70,08; -16,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,09; -21,8</t>
+          <t>-51,95; -19,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 8,44</t>
+          <t>-3,8; 9,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,49</t>
+          <t>-5,13; 8,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 13,14</t>
+          <t>-2,63; 12,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 22,94</t>
+          <t>-3,16; 8,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 80,74</t>
+          <t>-29,84; 88,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 38,58</t>
+          <t>-21,94; 41,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 86,34</t>
+          <t>-15,17; 83,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 381,31</t>
+          <t>-13,69; 46,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>-5,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>-26,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,77</t>
+          <t>-5,44; 0,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -4,48</t>
+          <t>-10,93; -4,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -4,08</t>
+          <t>-10,12; -3,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 43,19</t>
+          <t>-8,93; -2,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 4,9</t>
+          <t>-31,17; 6,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,94; -25,55</t>
+          <t>-54,41; -26,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; -23,59</t>
+          <t>-52,68; -22,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 226,94</t>
+          <t>-38,62; -13,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>8,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,02</t>
+          <t>-2,23; 6,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,4</t>
+          <t>1,66; 11,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,52</t>
+          <t>-1,98; 6,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 9,66</t>
+          <t>4,44; 12,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 73,22</t>
+          <t>-15,16; 67,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 74,21</t>
+          <t>7,37; 71,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 42,86</t>
+          <t>-10,06; 43,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 54,02</t>
+          <t>20,64; 78,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>27,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2353,55%</t>
+          <t>2304,7%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,27; 25,66</t>
+          <t>20,22; 25,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 32,97</t>
+          <t>26,72; 33,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,15; 30,25</t>
+          <t>24,34; 30,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 30,94</t>
+          <t>24,69; 30,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>629,73; 4200,02</t>
+          <t>618,83; 4244,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>813,38; 8331,85</t>
+          <t>746,07; 8198,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>750,81; 7885,53</t>
+          <t>894,41; 9234,42</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,88</t>
+          <t>2,39; 5,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,26</t>
+          <t>2,27; 6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,62</t>
+          <t>0,96; 4,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 22,38</t>
+          <t>0,12; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,83; 49,87</t>
+          <t>17,48; 49,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 39,9</t>
+          <t>12,2; 37,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 33,17</t>
+          <t>6,04; 34,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 134,27</t>
+          <t>0,62; 20,05</t>
         </is>
       </c>
     </row>
